--- a/artfynd/S 2227-2023 artfynd.xlsx
+++ b/artfynd/S 2227-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93260481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96852545</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103575490</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1178,6 +1198,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80523954</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1308,6 +1333,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92116920</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96782724</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1547,6 +1582,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96802033</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1655,6 +1695,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99804264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1753,6 +1798,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103575062</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1855,6 +1905,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103592659</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1957,6 +2012,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103592651</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2083,6 +2143,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80641671</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2204,6 +2269,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93261272</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2314,6 +2384,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96775219</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2435,6 +2510,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96904969</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2556,6 +2636,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96858059</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2672,6 +2757,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96902756</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2788,6 +2878,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105348599</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2893,6 +2988,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87812513</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3017,6 +3117,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96795831</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3135,6 +3240,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102565261</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3254,6 +3364,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100328808</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3378,6 +3493,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100400333</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3497,6 +3617,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96781710</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3616,6 +3741,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96807397</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3725,6 +3855,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105994649</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3844,6 +3979,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96789472</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3963,6 +4103,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96795832</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4082,6 +4227,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96887777</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4210,6 +4360,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99173519</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4322,6 +4477,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99804395</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4435,6 +4595,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105348881</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4538,6 +4703,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102057865</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4641,6 +4811,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102057943</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4743,6 +4918,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93398981</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4854,8 +5034,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97258755</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>